--- a/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/75.xlsx
+++ b/estimation/notsensor/DenseModel/Dense_1st_torch_optimized/IWALQQ_1st_correction/angle/1_fold/75.xlsx
@@ -426,13 +426,13 @@
         <v>-7.935276163821345</v>
       </c>
       <c r="E2">
-        <v>-7.651261946853354</v>
+        <v>-6.347115774332383</v>
       </c>
       <c r="F2">
-        <v>-5.668624315632083</v>
+        <v>-5.808241499536925</v>
       </c>
       <c r="G2">
-        <v>-5.295960302933394</v>
+        <v>-6.537878356535588</v>
       </c>
     </row>
     <row r="3" spans="1:7">
@@ -449,13 +449,13 @@
         <v>-7.712478890994617</v>
       </c>
       <c r="E3">
-        <v>-8.012856067891823</v>
+        <v>-7.323364200905958</v>
       </c>
       <c r="F3">
-        <v>-5.786971509735243</v>
+        <v>-5.718221157139898</v>
       </c>
       <c r="G3">
-        <v>-5.517488768239265</v>
+        <v>-6.392121657532556</v>
       </c>
     </row>
     <row r="4" spans="1:7">
@@ -472,13 +472,13 @@
         <v>-7.632769355025677</v>
       </c>
       <c r="E4">
-        <v>-8.206326062921525</v>
+        <v>-7.824829298619343</v>
       </c>
       <c r="F4">
-        <v>-5.722744043159183</v>
+        <v>-5.866691103478459</v>
       </c>
       <c r="G4">
-        <v>-5.517770164610103</v>
+        <v>-6.515482515962418</v>
       </c>
     </row>
     <row r="5" spans="1:7">
@@ -495,13 +495,13 @@
         <v>-7.714219244772184</v>
       </c>
       <c r="E5">
-        <v>-9.338249840456784</v>
+        <v>-8.929120327759797</v>
       </c>
       <c r="F5">
-        <v>-5.60401414331593</v>
+        <v>-5.824845295758639</v>
       </c>
       <c r="G5">
-        <v>-5.954258972871931</v>
+        <v>-6.48658476395012</v>
       </c>
     </row>
     <row r="6" spans="1:7">
@@ -518,13 +518,13 @@
         <v>-7.920873586603483</v>
       </c>
       <c r="E6">
-        <v>-11.23757788027988</v>
+        <v>-9.780817605226408</v>
       </c>
       <c r="F6">
-        <v>-5.504136228825588</v>
+        <v>-5.51076482478279</v>
       </c>
       <c r="G6">
-        <v>-6.7335978088173</v>
+        <v>-6.140069962354604</v>
       </c>
     </row>
     <row r="7" spans="1:7">
@@ -541,13 +541,13 @@
         <v>-8.219727767892888</v>
       </c>
       <c r="E7">
-        <v>-11.26528761273281</v>
+        <v>-11.07634156323677</v>
       </c>
       <c r="F7">
-        <v>-5.258569197367883</v>
+        <v>-5.555657367810106</v>
       </c>
       <c r="G7">
-        <v>-5.690458151575106</v>
+        <v>-6.781067721304909</v>
       </c>
     </row>
     <row r="8" spans="1:7">
@@ -564,13 +564,13 @@
         <v>-8.573793441703096</v>
       </c>
       <c r="E8">
-        <v>-13.01050715360088</v>
+        <v>-11.23192634471831</v>
       </c>
       <c r="F8">
-        <v>-5.373038803658538</v>
+        <v>-5.643026934518176</v>
       </c>
       <c r="G8">
-        <v>-6.931061918598209</v>
+        <v>-6.510685535476014</v>
       </c>
     </row>
     <row r="9" spans="1:7">
@@ -587,13 +587,13 @@
         <v>-8.946965965889396</v>
       </c>
       <c r="E9">
-        <v>-12.46142515169684</v>
+        <v>-12.31944390613435</v>
       </c>
       <c r="F9">
-        <v>-5.293973620163534</v>
+        <v>-5.373266604694308</v>
       </c>
       <c r="G9">
-        <v>-5.485108322319654</v>
+        <v>-6.79914329994933</v>
       </c>
     </row>
     <row r="10" spans="1:7">
@@ -610,13 +610,13 @@
         <v>-9.305306898170601</v>
       </c>
       <c r="E10">
-        <v>-13.43650976045044</v>
+        <v>-12.7972160278396</v>
       </c>
       <c r="F10">
-        <v>-5.19041692603736</v>
+        <v>-5.285267478760111</v>
       </c>
       <c r="G10">
-        <v>-5.46368578213503</v>
+        <v>-6.401808313780463</v>
       </c>
     </row>
     <row r="11" spans="1:7">
@@ -633,13 +633,13 @@
         <v>-9.623446726392769</v>
       </c>
       <c r="E11">
-        <v>-13.84581588363373</v>
+        <v>-13.71009298914984</v>
       </c>
       <c r="F11">
-        <v>-4.734132279757724</v>
+        <v>-5.012243381369213</v>
       </c>
       <c r="G11">
-        <v>-5.231672819106287</v>
+        <v>-6.404936779315074</v>
       </c>
     </row>
     <row r="12" spans="1:7">
@@ -656,13 +656,13 @@
         <v>-9.877339517497733</v>
       </c>
       <c r="E12">
-        <v>-15.29304824937506</v>
+        <v>-14.63564967768155</v>
       </c>
       <c r="F12">
-        <v>-4.63318245784816</v>
+        <v>-4.775003927411852</v>
       </c>
       <c r="G12">
-        <v>-5.234208696989369</v>
+        <v>-6.407459415015999</v>
       </c>
     </row>
     <row r="13" spans="1:7">
@@ -679,13 +679,13 @@
         <v>-10.05359405721178</v>
       </c>
       <c r="E13">
-        <v>-15.68206228052997</v>
+        <v>-16.38530259460313</v>
       </c>
       <c r="F13">
-        <v>-4.744980579264786</v>
+        <v>-4.488693645247453</v>
       </c>
       <c r="G13">
-        <v>-5.386834777986389</v>
+        <v>-6.286247100641123</v>
       </c>
     </row>
     <row r="14" spans="1:7">
@@ -702,13 +702,13 @@
         <v>-10.14870724071709</v>
       </c>
       <c r="E14">
-        <v>-17.07050599670373</v>
+        <v>-16.87930929562588</v>
       </c>
       <c r="F14">
-        <v>-4.561586663224198</v>
+        <v>-4.556831005964726</v>
       </c>
       <c r="G14">
-        <v>-5.22371095708434</v>
+        <v>-5.775330607565402</v>
       </c>
     </row>
     <row r="15" spans="1:7">
@@ -725,13 +725,13 @@
         <v>-10.16211666231912</v>
       </c>
       <c r="E15">
-        <v>-18.14073837283249</v>
+        <v>-17.93875484666837</v>
       </c>
       <c r="F15">
-        <v>-4.310304725054579</v>
+        <v>-4.398201961798232</v>
       </c>
       <c r="G15">
-        <v>-4.235668709252236</v>
+        <v>-5.528794281255876</v>
       </c>
     </row>
     <row r="16" spans="1:7">
@@ -748,13 +748,13 @@
         <v>-10.10297387291348</v>
       </c>
       <c r="E16">
-        <v>-19.12223530078096</v>
+        <v>-18.41803042174417</v>
       </c>
       <c r="F16">
-        <v>-4.065589255286953</v>
+        <v>-3.696127453229539</v>
       </c>
       <c r="G16">
-        <v>-4.135686923420708</v>
+        <v>-5.456303265582455</v>
       </c>
     </row>
     <row r="17" spans="1:7">
@@ -771,13 +771,13 @@
         <v>-9.985131601864024</v>
       </c>
       <c r="E17">
-        <v>-20.48431424128206</v>
+        <v>-19.68811341277945</v>
       </c>
       <c r="F17">
-        <v>-3.971936521828649</v>
+        <v>-3.780711220361994</v>
       </c>
       <c r="G17">
-        <v>-3.787056683225598</v>
+        <v>-4.962061990388042</v>
       </c>
     </row>
     <row r="18" spans="1:7">
@@ -794,13 +794,13 @@
         <v>-9.825453938920505</v>
       </c>
       <c r="E18">
-        <v>-20.93593895406702</v>
+        <v>-20.44994765203785</v>
       </c>
       <c r="F18">
-        <v>-3.824287487586262</v>
+        <v>-3.442349644075286</v>
       </c>
       <c r="G18">
-        <v>-4.491150129608872</v>
+        <v>-4.914939685182055</v>
       </c>
     </row>
     <row r="19" spans="1:7">
@@ -817,13 +817,13 @@
         <v>-9.643946194092715</v>
       </c>
       <c r="E19">
-        <v>-21.05496083641062</v>
+        <v>-20.96465853622367</v>
       </c>
       <c r="F19">
-        <v>-3.388842080058855</v>
+        <v>-3.123593867478036</v>
       </c>
       <c r="G19">
-        <v>-4.032536945508095</v>
+        <v>-4.68066893009553</v>
       </c>
     </row>
     <row r="20" spans="1:7">
@@ -840,13 +840,13 @@
         <v>-9.45725967772192</v>
       </c>
       <c r="E20">
-        <v>-21.03533895853539</v>
+        <v>-22.28153877765421</v>
       </c>
       <c r="F20">
-        <v>-3.074729302754296</v>
+        <v>-2.61504172318396</v>
       </c>
       <c r="G20">
-        <v>-3.665142533196397</v>
+        <v>-5.264579641766643</v>
       </c>
     </row>
     <row r="21" spans="1:7">
@@ -863,13 +863,13 @@
         <v>-9.278497567983386</v>
       </c>
       <c r="E21">
-        <v>-23.11605049626171</v>
+        <v>-23.30949332044736</v>
       </c>
       <c r="F21">
-        <v>-2.560420005010764</v>
+        <v>-2.581293206826506</v>
       </c>
       <c r="G21">
-        <v>-3.295053336815732</v>
+        <v>-4.623019090074662</v>
       </c>
     </row>
     <row r="22" spans="1:7">
@@ -886,13 +886,13 @@
         <v>-9.120223057874679</v>
       </c>
       <c r="E22">
-        <v>-23.10136918352884</v>
+        <v>-23.09995629963845</v>
       </c>
       <c r="F22">
-        <v>-2.475282060085836</v>
+        <v>-2.403591003210553</v>
       </c>
       <c r="G22">
-        <v>-3.943705077052832</v>
+        <v>-4.868383483263285</v>
       </c>
     </row>
     <row r="23" spans="1:7">
@@ -909,13 +909,13 @@
         <v>-8.987416505170748</v>
       </c>
       <c r="E23">
-        <v>-24.52449648212734</v>
+        <v>-23.90492425381991</v>
       </c>
       <c r="F23">
-        <v>-2.405384418637614</v>
+        <v>-1.998583955899013</v>
       </c>
       <c r="G23">
-        <v>-3.329929934071954</v>
+        <v>-5.496009948780474</v>
       </c>
     </row>
     <row r="24" spans="1:7">
@@ -932,13 +932,13 @@
         <v>-8.879389649478982</v>
       </c>
       <c r="E24">
-        <v>-24.66679019239636</v>
+        <v>-24.57962612469672</v>
       </c>
       <c r="F24">
-        <v>-2.537687118375737</v>
+        <v>-1.686430267502076</v>
       </c>
       <c r="G24">
-        <v>-4.320037962320563</v>
+        <v>-4.446199542276648</v>
       </c>
     </row>
     <row r="25" spans="1:7">
@@ -955,13 +955,13 @@
         <v>-8.793864257823172</v>
       </c>
       <c r="E25">
-        <v>-23.48351351961412</v>
+        <v>-25.266998665847</v>
       </c>
       <c r="F25">
-        <v>-2.085583242378032</v>
+        <v>-1.735942615534805</v>
       </c>
       <c r="G25">
-        <v>-3.898992848999435</v>
+        <v>-4.895559751595162</v>
       </c>
     </row>
     <row r="26" spans="1:7">
@@ -978,13 +978,13 @@
         <v>-8.715100135652515</v>
       </c>
       <c r="E26">
-        <v>-24.9716878188588</v>
+        <v>-25.34537296549775</v>
       </c>
       <c r="F26">
-        <v>-1.581288078166943</v>
+        <v>-1.472641066350565</v>
       </c>
       <c r="G26">
-        <v>-3.381336085205757</v>
+        <v>-4.818006911792195</v>
       </c>
     </row>
     <row r="27" spans="1:7">
@@ -1001,13 +1001,13 @@
         <v>-8.616516486489532</v>
       </c>
       <c r="E27">
-        <v>-24.61709924711019</v>
+        <v>-24.45667805538847</v>
       </c>
       <c r="F27">
-        <v>-1.826532874704959</v>
+        <v>-1.553205594844637</v>
       </c>
       <c r="G27">
-        <v>-4.878275393334627</v>
+        <v>-5.026534864765348</v>
       </c>
     </row>
     <row r="28" spans="1:7">
@@ -1024,13 +1024,13 @@
         <v>-8.468287999990844</v>
       </c>
       <c r="E28">
-        <v>-25.24709602258329</v>
+        <v>-24.3922831549994</v>
       </c>
       <c r="F28">
-        <v>-1.934239689519159</v>
+        <v>-1.607756073421193</v>
       </c>
       <c r="G28">
-        <v>-4.398501202146829</v>
+        <v>-5.248953866821283</v>
       </c>
     </row>
     <row r="29" spans="1:7">
@@ -1047,13 +1047,13 @@
         <v>-8.236735400684097</v>
       </c>
       <c r="E29">
-        <v>-24.56612221520585</v>
+        <v>-24.43914833250478</v>
       </c>
       <c r="F29">
-        <v>-1.751359361268306</v>
+        <v>-1.680991207135294</v>
       </c>
       <c r="G29">
-        <v>-4.298943166144326</v>
+        <v>-5.054773818215331</v>
       </c>
     </row>
     <row r="30" spans="1:7">
@@ -1070,13 +1070,13 @@
         <v>-7.900092629101522</v>
       </c>
       <c r="E30">
-        <v>-24.25959886657466</v>
+        <v>-23.89261586146706</v>
       </c>
       <c r="F30">
-        <v>-2.110267762614054</v>
+        <v>-1.634807239327013</v>
       </c>
       <c r="G30">
-        <v>-4.580713628628315</v>
+        <v>-5.111711890945257</v>
       </c>
     </row>
     <row r="31" spans="1:7">
@@ -1093,13 +1093,13 @@
         <v>-7.452813167964933</v>
       </c>
       <c r="E31">
-        <v>-24.61100844956988</v>
+        <v>-23.70374226755515</v>
       </c>
       <c r="F31">
-        <v>-2.025474418528691</v>
+        <v>-1.890135752259308</v>
       </c>
       <c r="G31">
-        <v>-4.487422455331653</v>
+        <v>-4.839816785804913</v>
       </c>
     </row>
     <row r="32" spans="1:7">
@@ -1116,13 +1116,13 @@
         <v>-6.898031795316381</v>
       </c>
       <c r="E32">
-        <v>-23.06692108175249</v>
+        <v>-24.08839990671468</v>
       </c>
       <c r="F32">
-        <v>-1.878647124749881</v>
+        <v>-1.987375316571733</v>
       </c>
       <c r="G32">
-        <v>-3.550716837177028</v>
+        <v>-5.595667301149154</v>
       </c>
     </row>
     <row r="33" spans="1:7">
@@ -1139,13 +1139,13 @@
         <v>-6.258577666298023</v>
       </c>
       <c r="E33">
-        <v>-23.1720133780485</v>
+        <v>-24.1087191695871</v>
       </c>
       <c r="F33">
-        <v>-1.741727933475957</v>
+        <v>-1.916516768936263</v>
       </c>
       <c r="G33">
-        <v>-4.293742299102131</v>
+        <v>-5.191532454442624</v>
       </c>
     </row>
     <row r="34" spans="1:7">
@@ -1162,13 +1162,13 @@
         <v>-5.564966728815414</v>
       </c>
       <c r="E34">
-        <v>-22.88693688231763</v>
+        <v>-22.76200986986803</v>
       </c>
       <c r="F34">
-        <v>-2.073328375021016</v>
+        <v>-1.953549762045818</v>
       </c>
       <c r="G34">
-        <v>-4.142423883593124</v>
+        <v>-4.856968722243878</v>
       </c>
     </row>
     <row r="35" spans="1:7">
@@ -1185,13 +1185,13 @@
         <v>-4.850348518797907</v>
       </c>
       <c r="E35">
-        <v>-23.49012056319131</v>
+        <v>-22.07267649947244</v>
       </c>
       <c r="F35">
-        <v>-2.269648136014887</v>
+        <v>-1.89938613104637</v>
       </c>
       <c r="G35">
-        <v>-3.73812350960963</v>
+        <v>-5.125321543657201</v>
       </c>
     </row>
     <row r="36" spans="1:7">
@@ -1208,13 +1208,13 @@
         <v>-4.155342318327346</v>
       </c>
       <c r="E36">
-        <v>-21.06784887343645</v>
+        <v>-21.99095565753002</v>
       </c>
       <c r="F36">
-        <v>-2.234861675301725</v>
+        <v>-1.946328055028212</v>
       </c>
       <c r="G36">
-        <v>-4.201500568741419</v>
+        <v>-4.859219893210582</v>
       </c>
     </row>
     <row r="37" spans="1:7">
@@ -1231,13 +1231,13 @@
         <v>-3.511546772018017</v>
       </c>
       <c r="E37">
-        <v>-21.22889499457123</v>
+        <v>-21.77105748819155</v>
       </c>
       <c r="F37">
-        <v>-2.095922095932372</v>
+        <v>-1.762262333023954</v>
       </c>
       <c r="G37">
-        <v>-4.294288539116112</v>
+        <v>-4.526116111594654</v>
       </c>
     </row>
     <row r="38" spans="1:7">
@@ -1254,13 +1254,13 @@
         <v>-2.944020609457727</v>
       </c>
       <c r="E38">
-        <v>-21.31491788682094</v>
+        <v>-21.41897316256919</v>
       </c>
       <c r="F38">
-        <v>-2.125760718148613</v>
+        <v>-2.066337782508791</v>
       </c>
       <c r="G38">
-        <v>-2.52222303340057</v>
+        <v>-4.294771878764845</v>
       </c>
     </row>
     <row r="39" spans="1:7">
@@ -1277,13 +1277,13 @@
         <v>-2.473864913930786</v>
       </c>
       <c r="E39">
-        <v>-21.82721056588666</v>
+        <v>-21.2462345215466</v>
       </c>
       <c r="F39">
-        <v>-1.930214652308956</v>
+        <v>-2.244720075762442</v>
       </c>
       <c r="G39">
-        <v>-3.894477264883869</v>
+        <v>-3.744291055949293</v>
       </c>
     </row>
     <row r="40" spans="1:7">
@@ -1300,13 +1300,13 @@
         <v>-2.10858824221491</v>
       </c>
       <c r="E40">
-        <v>-21.6631620664848</v>
+        <v>-20.87779787628254</v>
       </c>
       <c r="F40">
-        <v>-1.812134192509498</v>
+        <v>-2.512655512197942</v>
       </c>
       <c r="G40">
-        <v>-2.58186251129054</v>
+        <v>-4.057240236322137</v>
       </c>
     </row>
     <row r="41" spans="1:7">
@@ -1323,13 +1323,13 @@
         <v>-1.850349673303501</v>
       </c>
       <c r="E41">
-        <v>-20.76116702821499</v>
+        <v>-19.66742734351241</v>
       </c>
       <c r="F41">
-        <v>-2.068851049208884</v>
+        <v>-2.128608645279438</v>
       </c>
       <c r="G41">
-        <v>-3.52599699363529</v>
+        <v>-3.623591876133005</v>
       </c>
     </row>
     <row r="42" spans="1:7">
@@ -1346,13 +1346,13 @@
         <v>-1.692834581003724</v>
       </c>
       <c r="E42">
-        <v>-19.29385540872365</v>
+        <v>-18.96952157182029</v>
       </c>
       <c r="F42">
-        <v>-1.922066002167617</v>
+        <v>-2.29844881387542</v>
       </c>
       <c r="G42">
-        <v>-3.332333390133465</v>
+        <v>-3.721948184104751</v>
       </c>
     </row>
     <row r="43" spans="1:7">
@@ -1369,13 +1369,13 @@
         <v>-1.619363383168522</v>
       </c>
       <c r="E43">
-        <v>-18.60247063960258</v>
+        <v>-19.0529496484636</v>
       </c>
       <c r="F43">
-        <v>-2.552279638543453</v>
+        <v>-2.291934532619805</v>
       </c>
       <c r="G43">
-        <v>-2.967905226624953</v>
+        <v>-3.359274609732053</v>
       </c>
     </row>
     <row r="44" spans="1:7">
@@ -1392,13 +1392,13 @@
         <v>-1.614969864571608</v>
       </c>
       <c r="E44">
-        <v>-17.96390146283296</v>
+        <v>-16.90183392534003</v>
       </c>
       <c r="F44">
-        <v>-2.285753255060115</v>
+        <v>-2.394153413390459</v>
       </c>
       <c r="G44">
-        <v>-2.677759083926608</v>
+        <v>-3.329062571140665</v>
       </c>
     </row>
     <row r="45" spans="1:7">
@@ -1415,13 +1415,13 @@
         <v>-1.659271463784021</v>
       </c>
       <c r="E45">
-        <v>-17.55075972216519</v>
+        <v>-17.30116382028442</v>
       </c>
       <c r="F45">
-        <v>-2.004944160817708</v>
+        <v>-2.224555956443496</v>
       </c>
       <c r="G45">
-        <v>-3.149369469814564</v>
+        <v>-3.243028113666085</v>
       </c>
     </row>
     <row r="46" spans="1:7">
@@ -1438,13 +1438,13 @@
         <v>-1.732917106646111</v>
       </c>
       <c r="E46">
-        <v>-17.97465658860119</v>
+        <v>-17.45619612793701</v>
       </c>
       <c r="F46">
-        <v>-2.542852817499595</v>
+        <v>-2.313571489180928</v>
       </c>
       <c r="G46">
-        <v>-3.025525271735968</v>
+        <v>-2.924490732422951</v>
       </c>
     </row>
     <row r="47" spans="1:7">
@@ -1461,13 +1461,13 @@
         <v>-1.820845990037575</v>
       </c>
       <c r="E47">
-        <v>-17.22039848635762</v>
+        <v>-16.08664520532326</v>
       </c>
       <c r="F47">
-        <v>-2.211940749266263</v>
+        <v>-2.413099832627289</v>
       </c>
       <c r="G47">
-        <v>-2.215411604457534</v>
+        <v>-2.741718823745328</v>
       </c>
     </row>
     <row r="48" spans="1:7">
@@ -1484,13 +1484,13 @@
         <v>-1.909609273136489</v>
       </c>
       <c r="E48">
-        <v>-15.77168530961578</v>
+        <v>-15.56233395624118</v>
       </c>
       <c r="F48">
-        <v>-2.499787652962854</v>
+        <v>-2.586794394748498</v>
       </c>
       <c r="G48">
-        <v>-2.419599432228702</v>
+        <v>-3.111569660847166</v>
       </c>
     </row>
     <row r="49" spans="1:7">
@@ -1507,13 +1507,13 @@
         <v>-1.991985538896599</v>
       </c>
       <c r="E49">
-        <v>-15.15709893119079</v>
+        <v>-15.4488186982909</v>
       </c>
       <c r="F49">
-        <v>-2.313704856332779</v>
+        <v>-2.583042718781218</v>
       </c>
       <c r="G49">
-        <v>-2.554974260420579</v>
+        <v>-2.622320688325973</v>
       </c>
     </row>
     <row r="50" spans="1:7">
@@ -1530,13 +1530,13 @@
         <v>-2.065621272288019</v>
       </c>
       <c r="E50">
-        <v>-14.62850827417146</v>
+        <v>-14.27017465441851</v>
       </c>
       <c r="F50">
-        <v>-2.417613606605143</v>
+        <v>-2.994889595737674</v>
       </c>
       <c r="G50">
-        <v>-2.187881107752955</v>
+        <v>-2.639542146221262</v>
       </c>
     </row>
     <row r="51" spans="1:7">
@@ -1553,13 +1553,13 @@
         <v>-2.136249837982683</v>
       </c>
       <c r="E51">
-        <v>-14.28496012205355</v>
+        <v>-14.31325855612748</v>
       </c>
       <c r="F51">
-        <v>-2.476171726676443</v>
+        <v>-2.853639699681914</v>
       </c>
       <c r="G51">
-        <v>-3.848245496427947</v>
+        <v>-2.576803997706534</v>
       </c>
     </row>
     <row r="52" spans="1:7">
@@ -1576,13 +1576,13 @@
         <v>-2.215691918320304</v>
       </c>
       <c r="E52">
-        <v>-15.17555699124605</v>
+        <v>-13.22051060723258</v>
       </c>
       <c r="F52">
-        <v>-2.886108388402043</v>
+        <v>-2.861945739629784</v>
       </c>
       <c r="G52">
-        <v>-3.086724016574935</v>
+        <v>-2.564359657024413</v>
       </c>
     </row>
     <row r="53" spans="1:7">
@@ -1599,13 +1599,13 @@
         <v>-2.31530413935086</v>
       </c>
       <c r="E53">
-        <v>-14.62427867944829</v>
+        <v>-12.73351851244771</v>
       </c>
       <c r="F53">
-        <v>-2.924064182798316</v>
+        <v>-2.768901027845135</v>
       </c>
       <c r="G53">
-        <v>-1.792598659818436</v>
+        <v>-2.802990400586159</v>
       </c>
     </row>
     <row r="54" spans="1:7">
@@ -1622,13 +1622,13 @@
         <v>-2.450000903388962</v>
       </c>
       <c r="E54">
-        <v>-13.18046078310874</v>
+        <v>-11.90278354116261</v>
       </c>
       <c r="F54">
-        <v>-2.328549200190946</v>
+        <v>-2.978350412173379</v>
       </c>
       <c r="G54">
-        <v>-2.107921501342938</v>
+        <v>-2.381683754167429</v>
       </c>
     </row>
     <row r="55" spans="1:7">
@@ -1645,13 +1645,13 @@
         <v>-2.629258610262044</v>
       </c>
       <c r="E55">
-        <v>-12.3194167352903</v>
+        <v>-11.56874518446081</v>
       </c>
       <c r="F55">
-        <v>-2.954375802801556</v>
+        <v>-2.818405920571239</v>
       </c>
       <c r="G55">
-        <v>-2.526857797155549</v>
+        <v>-2.284605316773841</v>
       </c>
     </row>
     <row r="56" spans="1:7">
@@ -1668,13 +1668,13 @@
         <v>-2.857236918675864</v>
       </c>
       <c r="E56">
-        <v>-12.62997495426233</v>
+        <v>-11.00656230725258</v>
       </c>
       <c r="F56">
-        <v>-2.838733228268536</v>
+        <v>-2.95611703108224</v>
       </c>
       <c r="G56">
-        <v>-2.16691873339829</v>
+        <v>-2.202397849942659</v>
       </c>
     </row>
     <row r="57" spans="1:7">
@@ -1691,13 +1691,13 @@
         <v>-3.136918452880557</v>
       </c>
       <c r="E57">
-        <v>-12.09590484369372</v>
+        <v>-11.19518230662007</v>
       </c>
       <c r="F57">
-        <v>-3.122717454765874</v>
+        <v>-3.130810604291225</v>
       </c>
       <c r="G57">
-        <v>-2.997087685553629</v>
+        <v>-2.805201845006392</v>
       </c>
     </row>
     <row r="58" spans="1:7">
@@ -1714,13 +1714,13 @@
         <v>-3.463798659765077</v>
       </c>
       <c r="E58">
-        <v>-11.51511446678797</v>
+        <v>-10.22408728346722</v>
       </c>
       <c r="F58">
-        <v>-2.945935567334431</v>
+        <v>-3.100508096329416</v>
       </c>
       <c r="G58">
-        <v>-3.150779762214293</v>
+        <v>-2.318220596179601</v>
       </c>
     </row>
     <row r="59" spans="1:7">
@@ -1737,13 +1737,13 @@
         <v>-3.831496641569293</v>
       </c>
       <c r="E59">
-        <v>-11.45702773069158</v>
+        <v>-9.770311545528614</v>
       </c>
       <c r="F59">
-        <v>-3.206468712658515</v>
+        <v>-3.216637750895282</v>
       </c>
       <c r="G59">
-        <v>-2.532101701289755</v>
+        <v>-2.645262768913122</v>
       </c>
     </row>
     <row r="60" spans="1:7">
@@ -1760,13 +1760,13 @@
         <v>-4.23029804724519</v>
       </c>
       <c r="E60">
-        <v>-9.708506932271927</v>
+        <v>-9.564795809638509</v>
       </c>
       <c r="F60">
-        <v>-2.839434027091305</v>
+        <v>-2.847558654577962</v>
       </c>
       <c r="G60">
-        <v>-2.555851554988486</v>
+        <v>-2.295033535222545</v>
       </c>
     </row>
     <row r="61" spans="1:7">
@@ -1783,13 +1783,13 @@
         <v>-4.643385873588803</v>
       </c>
       <c r="E61">
-        <v>-10.17480842931575</v>
+        <v>-8.569405523434511</v>
       </c>
       <c r="F61">
-        <v>-3.290652378335418</v>
+        <v>-2.814254143148408</v>
       </c>
       <c r="G61">
-        <v>-2.842104496132648</v>
+        <v>-3.067304356441571</v>
       </c>
     </row>
     <row r="62" spans="1:7">
@@ -1806,13 +1806,13 @@
         <v>-5.055963683500142</v>
       </c>
       <c r="E62">
-        <v>-10.02882854120449</v>
+        <v>-8.022959093402937</v>
       </c>
       <c r="F62">
-        <v>-2.827339863010432</v>
+        <v>-2.789244902890488</v>
       </c>
       <c r="G62">
-        <v>-2.235463578788899</v>
+        <v>-2.491587244980154</v>
       </c>
     </row>
     <row r="63" spans="1:7">
@@ -1829,13 +1829,13 @@
         <v>-5.45169569417244</v>
       </c>
       <c r="E63">
-        <v>-9.905731032253987</v>
+        <v>-8.277531788218134</v>
       </c>
       <c r="F63">
-        <v>-2.827494767714755</v>
+        <v>-2.86547458476571</v>
       </c>
       <c r="G63">
-        <v>-3.310083213564023</v>
+        <v>-2.820625676673857</v>
       </c>
     </row>
     <row r="64" spans="1:7">
@@ -1852,13 +1852,13 @@
         <v>-5.81221913522165</v>
       </c>
       <c r="E64">
-        <v>-8.898765966486383</v>
+        <v>-7.876145966074263</v>
       </c>
       <c r="F64">
-        <v>-3.09280096601377</v>
+        <v>-2.952502864103826</v>
       </c>
       <c r="G64">
-        <v>-2.45272144034911</v>
+        <v>-2.828676923425364</v>
       </c>
     </row>
     <row r="65" spans="1:7">
@@ -1875,13 +1875,13 @@
         <v>-6.125465565499093</v>
       </c>
       <c r="E65">
-        <v>-8.359524338601013</v>
+        <v>-8.716829994754219</v>
       </c>
       <c r="F65">
-        <v>-3.348401183454182</v>
+        <v>-3.136685385911879</v>
       </c>
       <c r="G65">
-        <v>-2.731062177654414</v>
+        <v>-3.126361178316629</v>
       </c>
     </row>
     <row r="66" spans="1:7">
@@ -1898,13 +1898,13 @@
         <v>-6.378557944181176</v>
       </c>
       <c r="E66">
-        <v>-9.376243737381138</v>
+        <v>-8.436553681471485</v>
       </c>
       <c r="F66">
-        <v>-3.165502631120468</v>
+        <v>-2.701882791489044</v>
       </c>
       <c r="G66">
-        <v>-3.268999343421668</v>
+        <v>-3.241343045986596</v>
       </c>
     </row>
     <row r="67" spans="1:7">
@@ -1921,13 +1921,13 @@
         <v>-6.560774594782032</v>
       </c>
       <c r="E67">
-        <v>-8.299426960045219</v>
+        <v>-7.433695941628839</v>
       </c>
       <c r="F67">
-        <v>-2.979487760617423</v>
+        <v>-3.059363915799768</v>
       </c>
       <c r="G67">
-        <v>-3.26562589751715</v>
+        <v>-2.81297831647814</v>
       </c>
     </row>
     <row r="68" spans="1:7">
@@ -1944,13 +1944,13 @@
         <v>-6.6653173797932</v>
       </c>
       <c r="E68">
-        <v>-9.321028053805614</v>
+        <v>-7.881204271540831</v>
       </c>
       <c r="F68">
-        <v>-2.794143867710645</v>
+        <v>-3.299719687926461</v>
       </c>
       <c r="G68">
-        <v>-2.703445606765813</v>
+        <v>-2.228028093507696</v>
       </c>
     </row>
     <row r="69" spans="1:7">
@@ -1967,13 +1967,13 @@
         <v>-6.688815399830583</v>
       </c>
       <c r="E69">
-        <v>-9.858562446990092</v>
+        <v>-7.277495287682266</v>
       </c>
       <c r="F69">
-        <v>-3.264491707387607</v>
+        <v>-3.235995040363901</v>
       </c>
       <c r="G69">
-        <v>-3.040518732483327</v>
+        <v>-2.227299773489057</v>
       </c>
     </row>
     <row r="70" spans="1:7">
@@ -1990,13 +1990,13 @@
         <v>-6.637542509903011</v>
       </c>
       <c r="E70">
-        <v>-7.764532667207212</v>
+        <v>-7.687444454174639</v>
       </c>
       <c r="F70">
-        <v>-3.252766995168383</v>
+        <v>-3.236925296957245</v>
       </c>
       <c r="G70">
-        <v>-3.154053891752633</v>
+        <v>-2.584527500449653</v>
       </c>
     </row>
     <row r="71" spans="1:7">
@@ -2013,13 +2013,13 @@
         <v>-6.523146760813585</v>
       </c>
       <c r="E71">
-        <v>-8.722979662456636</v>
+        <v>-7.219775357980499</v>
       </c>
       <c r="F71">
-        <v>-3.198112970666477</v>
+        <v>-3.315599491038128</v>
       </c>
       <c r="G71">
-        <v>-2.592373493377726</v>
+        <v>-2.700068850315757</v>
       </c>
     </row>
     <row r="72" spans="1:7">
@@ -2036,13 +2036,13 @@
         <v>-6.356259149540589</v>
       </c>
       <c r="E72">
-        <v>-9.495673182385429</v>
+        <v>-7.092162960444348</v>
       </c>
       <c r="F72">
-        <v>-3.341886073831164</v>
+        <v>-3.623716545081224</v>
       </c>
       <c r="G72">
-        <v>-3.004890641389691</v>
+        <v>-2.661974402795364</v>
       </c>
     </row>
     <row r="73" spans="1:7">
@@ -2059,13 +2059,13 @@
         <v>-6.144447538017937</v>
       </c>
       <c r="E73">
-        <v>-9.706265337638131</v>
+        <v>-7.480950567898879</v>
       </c>
       <c r="F73">
-        <v>-3.29560932887377</v>
+        <v>-3.365012434982521</v>
       </c>
       <c r="G73">
-        <v>-3.220215144354967</v>
+        <v>-3.05544929286544</v>
       </c>
     </row>
     <row r="74" spans="1:7">
@@ -2082,13 +2082,13 @@
         <v>-5.894936117066003</v>
       </c>
       <c r="E74">
-        <v>-10.08601411097335</v>
+        <v>-7.875896900003841</v>
       </c>
       <c r="F74">
-        <v>-3.151647357941244</v>
+        <v>-3.456496502580296</v>
       </c>
       <c r="G74">
-        <v>-2.140047035256025</v>
+        <v>-2.4623054696853</v>
       </c>
     </row>
     <row r="75" spans="1:7">
@@ -2105,13 +2105,13 @@
         <v>-5.611070080444785</v>
       </c>
       <c r="E75">
-        <v>-10.28783008359919</v>
+        <v>-8.102823261002211</v>
       </c>
       <c r="F75">
-        <v>-3.353859296271228</v>
+        <v>-3.636411275529126</v>
       </c>
       <c r="G75">
-        <v>-1.734515138331923</v>
+        <v>-1.076501175309764</v>
       </c>
     </row>
     <row r="76" spans="1:7">
@@ -2128,13 +2128,13 @@
         <v>-5.294654506450208</v>
       </c>
       <c r="E76">
-        <v>-9.388502316519903</v>
+        <v>-8.228121608320443</v>
       </c>
       <c r="F76">
-        <v>-3.85645382220437</v>
+        <v>-3.658454132117621</v>
       </c>
       <c r="G76">
-        <v>-2.012451989081435</v>
+        <v>-1.295132913268772</v>
       </c>
     </row>
     <row r="77" spans="1:7">
@@ -2151,13 +2151,13 @@
         <v>-4.951189754346938</v>
       </c>
       <c r="E77">
-        <v>-9.179513241065916</v>
+        <v>-8.964818288362263</v>
       </c>
       <c r="F77">
-        <v>-3.545073828961647</v>
+        <v>-3.944929259395177</v>
       </c>
       <c r="G77">
-        <v>-1.243518197765995</v>
+        <v>-1.260600612748634</v>
       </c>
     </row>
     <row r="78" spans="1:7">
@@ -2174,13 +2174,13 @@
         <v>-4.584428120264215</v>
       </c>
       <c r="E78">
-        <v>-10.08191584199641</v>
+        <v>-8.839257289551588</v>
       </c>
       <c r="F78">
-        <v>-3.83320817614701</v>
+        <v>-3.91869900558553</v>
       </c>
       <c r="G78">
-        <v>-0.9590099141210292</v>
+        <v>-1.33693186124761</v>
       </c>
     </row>
     <row r="79" spans="1:7">
@@ -2197,13 +2197,13 @@
         <v>-4.200435290604313</v>
       </c>
       <c r="E79">
-        <v>-12.43763254926054</v>
+        <v>-9.742837293724078</v>
       </c>
       <c r="F79">
-        <v>-4.179691066450765</v>
+        <v>-3.81334144072567</v>
       </c>
       <c r="G79">
-        <v>-0.4567107710840298</v>
+        <v>-0.2404791786409929</v>
       </c>
     </row>
     <row r="80" spans="1:7">
@@ -2220,13 +2220,13 @@
         <v>-3.809072768380014</v>
       </c>
       <c r="E80">
-        <v>-11.18211313063393</v>
+        <v>-10.09267096776463</v>
       </c>
       <c r="F80">
-        <v>-4.044838651846825</v>
+        <v>-4.357984724392316</v>
       </c>
       <c r="G80">
-        <v>-1.718144490640227</v>
+        <v>-0.2345897181266295</v>
       </c>
     </row>
     <row r="81" spans="1:7">
@@ -2243,13 +2243,13 @@
         <v>-3.419909838889002</v>
       </c>
       <c r="E81">
-        <v>-11.71900448050932</v>
+        <v>-10.88880839763113</v>
       </c>
       <c r="F81">
-        <v>-4.436382243760664</v>
+        <v>-4.272226332282692</v>
       </c>
       <c r="G81">
-        <v>-0.5693156670567999</v>
+        <v>-0.1499423792330045</v>
       </c>
     </row>
     <row r="82" spans="1:7">
@@ -2266,13 +2266,13 @@
         <v>-3.049500536830679</v>
       </c>
       <c r="E82">
-        <v>-13.61434293473166</v>
+        <v>-11.25655671484602</v>
       </c>
       <c r="F82">
-        <v>-4.221825146026759</v>
+        <v>-4.600109060923987</v>
       </c>
       <c r="G82">
-        <v>-0.4159414027679051</v>
+        <v>0.3131433518913277</v>
       </c>
     </row>
     <row r="83" spans="1:7">
@@ -2289,13 +2289,13 @@
         <v>-2.714695019135573</v>
       </c>
       <c r="E83">
-        <v>-13.10549189591176</v>
+        <v>-12.79863796867801</v>
       </c>
       <c r="F83">
-        <v>-4.42957223534225</v>
+        <v>-4.910181062037689</v>
       </c>
       <c r="G83">
-        <v>-0.4071187989057474</v>
+        <v>0.7866043327357357</v>
       </c>
     </row>
     <row r="84" spans="1:7">
@@ -2312,13 +2312,13 @@
         <v>-2.431420906878849</v>
       </c>
       <c r="E84">
-        <v>-13.9413847990916</v>
+        <v>-13.57902989441984</v>
       </c>
       <c r="F84">
-        <v>-4.745890126673061</v>
+        <v>-4.959116037990667</v>
       </c>
       <c r="G84">
-        <v>0.3230882306912983</v>
+        <v>0.8051599404833507</v>
       </c>
     </row>
     <row r="85" spans="1:7">
@@ -2335,13 +2335,13 @@
         <v>-2.218133316096941</v>
       </c>
       <c r="E85">
-        <v>-15.72814856050603</v>
+        <v>-14.43035130854382</v>
       </c>
       <c r="F85">
-        <v>-5.009127063199882</v>
+        <v>-5.363825701404602</v>
       </c>
       <c r="G85">
-        <v>0.9587527007778375</v>
+        <v>1.032538139757114</v>
       </c>
     </row>
     <row r="86" spans="1:7">
@@ -2358,13 +2358,13 @@
         <v>-2.087526483221018</v>
       </c>
       <c r="E86">
-        <v>-16.39245305506124</v>
+        <v>-15.36068100867961</v>
       </c>
       <c r="F86">
-        <v>-4.950630242316389</v>
+        <v>-5.466455452407044</v>
       </c>
       <c r="G86">
-        <v>0.6583405563622129</v>
+        <v>1.972848942004005</v>
       </c>
     </row>
     <row r="87" spans="1:7">
@@ -2381,13 +2381,13 @@
         <v>-2.05377028282647</v>
       </c>
       <c r="E87">
-        <v>-17.69327985613459</v>
+        <v>-16.69576571562099</v>
       </c>
       <c r="F87">
-        <v>-5.273421824900078</v>
+        <v>-5.740127333106931</v>
       </c>
       <c r="G87">
-        <v>1.186216974235621</v>
+        <v>1.738227269090317</v>
       </c>
     </row>
     <row r="88" spans="1:7">
@@ -2404,13 +2404,13 @@
         <v>-2.127612126834627</v>
       </c>
       <c r="E88">
-        <v>-18.87348169506562</v>
+        <v>-18.33173129258</v>
       </c>
       <c r="F88">
-        <v>-5.472076753602441</v>
+        <v>-5.803624179633721</v>
       </c>
       <c r="G88">
-        <v>1.256814357860579</v>
+        <v>1.537671109775729</v>
       </c>
     </row>
     <row r="89" spans="1:7">
@@ -2427,13 +2427,13 @@
         <v>-2.315703977188518</v>
       </c>
       <c r="E89">
-        <v>-19.83968143781617</v>
+        <v>-19.6875564104765</v>
       </c>
       <c r="F89">
-        <v>-5.620213696245077</v>
+        <v>-5.828694719079448</v>
       </c>
       <c r="G89">
-        <v>1.228684652413392</v>
+        <v>1.665365472316497</v>
       </c>
     </row>
     <row r="90" spans="1:7">
@@ -2450,13 +2450,13 @@
         <v>-2.623121209818579</v>
       </c>
       <c r="E90">
-        <v>-22.54925763251367</v>
+        <v>-20.55256740152566</v>
       </c>
       <c r="F90">
-        <v>-6.091798288454419</v>
+        <v>-6.193532574294434</v>
       </c>
       <c r="G90">
-        <v>0.6159556418229238</v>
+        <v>2.461617885422003</v>
       </c>
     </row>
     <row r="91" spans="1:7">
@@ -2473,13 +2473,13 @@
         <v>-3.045394080386805</v>
       </c>
       <c r="E91">
-        <v>-24.77594000140324</v>
+        <v>-22.02135530354351</v>
       </c>
       <c r="F91">
-        <v>-5.776882823136548</v>
+        <v>-6.236898850382093</v>
       </c>
       <c r="G91">
-        <v>0.5522839194661211</v>
+        <v>1.69465386870243</v>
       </c>
     </row>
     <row r="92" spans="1:7">
@@ -2496,13 +2496,13 @@
         <v>-3.576898058050639</v>
       </c>
       <c r="E92">
-        <v>-25.90580785173902</v>
+        <v>-25.34440387206011</v>
       </c>
       <c r="F92">
-        <v>-5.998835585042647</v>
+        <v>-6.711385627787143</v>
       </c>
       <c r="G92">
-        <v>0.7170762553199623</v>
+        <v>1.661833120226095</v>
       </c>
     </row>
     <row r="93" spans="1:7">
@@ -2519,13 +2519,13 @@
         <v>-4.205600031885013</v>
       </c>
       <c r="E93">
-        <v>-27.6389363670066</v>
+        <v>-26.45455021809248</v>
       </c>
       <c r="F93">
-        <v>-6.304500671573456</v>
+        <v>-6.664045673268255</v>
       </c>
       <c r="G93">
-        <v>0.4195840120699749</v>
+        <v>1.167754061763106</v>
       </c>
     </row>
     <row r="94" spans="1:7">
@@ -2542,13 +2542,13 @@
         <v>-4.908207228193342</v>
       </c>
       <c r="E94">
-        <v>-29.76644515512819</v>
+        <v>-29.48638168012382</v>
       </c>
       <c r="F94">
-        <v>-6.585788562174682</v>
+        <v>-7.149398974263229</v>
       </c>
       <c r="G94">
-        <v>-0.5591721555244731</v>
+        <v>1.244840114645036</v>
       </c>
     </row>
     <row r="95" spans="1:7">
@@ -2565,13 +2565,13 @@
         <v>-5.66605746372096</v>
       </c>
       <c r="E95">
-        <v>-31.60923972543953</v>
+        <v>-31.79628834432635</v>
       </c>
       <c r="F95">
-        <v>-6.796122228705414</v>
+        <v>-7.335966365823942</v>
       </c>
       <c r="G95">
-        <v>-0.7328897221521893</v>
+        <v>0.3815326016415919</v>
       </c>
     </row>
     <row r="96" spans="1:7">
@@ -2588,13 +2588,13 @@
         <v>-6.452899685944103</v>
       </c>
       <c r="E96">
-        <v>-33.70523259870473</v>
+        <v>-33.59560956416405</v>
       </c>
       <c r="F96">
-        <v>-6.736857925423227</v>
+        <v>-7.252804491338392</v>
       </c>
       <c r="G96">
-        <v>-1.161241209478488</v>
+        <v>0.3075187350201059</v>
       </c>
     </row>
     <row r="97" spans="1:7">
@@ -2611,13 +2611,13 @@
         <v>-7.236343561754007</v>
       </c>
       <c r="E97">
-        <v>-37.20340404980895</v>
+        <v>-35.9392375100647</v>
       </c>
       <c r="F97">
-        <v>-7.039873892999884</v>
+        <v>-7.732586193182136</v>
       </c>
       <c r="G97">
-        <v>-1.006618869521288</v>
+        <v>0.02039843094465514</v>
       </c>
     </row>
     <row r="98" spans="1:7">
@@ -2634,13 +2634,13 @@
         <v>-7.993096982599123</v>
       </c>
       <c r="E98">
-        <v>-39.51037626285452</v>
+        <v>-38.3524975365443</v>
       </c>
       <c r="F98">
-        <v>-6.936515178682979</v>
+        <v>-7.595887347637357</v>
       </c>
       <c r="G98">
-        <v>-2.585729228480409</v>
+        <v>-1.447384902619854</v>
       </c>
     </row>
     <row r="99" spans="1:7">
@@ -2657,13 +2657,13 @@
         <v>-8.68237720515088</v>
       </c>
       <c r="E99">
-        <v>-42.14807651810227</v>
+        <v>-41.57981190030174</v>
       </c>
       <c r="F99">
-        <v>-7.351856109344442</v>
+        <v>-7.932059548878466</v>
       </c>
       <c r="G99">
-        <v>-2.521226559193249</v>
+        <v>-2.156566657496989</v>
       </c>
     </row>
     <row r="100" spans="1:7">
@@ -2680,13 +2680,13 @@
         <v>-9.286298582205701</v>
       </c>
       <c r="E100">
-        <v>-44.2800979305725</v>
+        <v>-43.09202333957914</v>
       </c>
       <c r="F100">
-        <v>-7.254054497749217</v>
+        <v>-7.787428257084478</v>
       </c>
       <c r="G100">
-        <v>-3.191469677437476</v>
+        <v>-2.965064778552259</v>
       </c>
     </row>
     <row r="101" spans="1:7">
@@ -2703,13 +2703,13 @@
         <v>-9.766162846583599</v>
       </c>
       <c r="E101">
-        <v>-45.92914626893968</v>
+        <v>-46.49491796179898</v>
       </c>
       <c r="F101">
-        <v>-7.416527166664701</v>
+        <v>-8.057633006019948</v>
       </c>
       <c r="G101">
-        <v>-4.726202173442666</v>
+        <v>-3.241346356532135</v>
       </c>
     </row>
     <row r="102" spans="1:7">
@@ -2726,13 +2726,13 @@
         <v>-10.12867129403798</v>
       </c>
       <c r="E102">
-        <v>-49.19188688485912</v>
+        <v>-48.13506332026707</v>
       </c>
       <c r="F102">
-        <v>-7.433657390370893</v>
+        <v>-8.170600782209327</v>
       </c>
       <c r="G102">
-        <v>-5.027279737511684</v>
+        <v>-4.234907283778204</v>
       </c>
     </row>
   </sheetData>
